--- a/data/Oficina_de_procuradora_de_mujeres/opmAgresores.xlsx
+++ b/data/Oficina_de_procuradora_de_mujeres/opmAgresores.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gnper\Documents\ViolenciaGeneroPR\data\Oficina_de_procuradora_de_mujeres\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E3566C5-A868-4395-9226-A79AC4DF4397}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A22B39B-D4D7-459D-BE27-CE3AAAE1D4F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5880" yWindow="2196" windowWidth="17280" windowHeight="9420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13056" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -89,7 +89,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -97,12 +97,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -631,7 +649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>2026</v>
       </c>
@@ -639,72 +657,72 @@
         <v>3</v>
       </c>
       <c r="C23">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>2026</v>
       </c>
       <c r="B24" t="s">
         <v>4</v>
       </c>
-      <c r="C24">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C24" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>2026</v>
       </c>
       <c r="B25" t="s">
         <v>5</v>
       </c>
-      <c r="C25">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C25" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>2026</v>
       </c>
       <c r="B26" t="s">
         <v>6</v>
       </c>
-      <c r="C26">
+      <c r="C26" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>2026</v>
       </c>
       <c r="B27" t="s">
         <v>7</v>
       </c>
-      <c r="C27">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C27" s="1">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>2026</v>
       </c>
       <c r="B28" t="s">
         <v>8</v>
       </c>
-      <c r="C28">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C28" s="1">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>2026</v>
       </c>
       <c r="B29" t="s">
         <v>9</v>
       </c>
-      <c r="C29">
+      <c r="C29" s="1">
         <v>0</v>
       </c>
     </row>

--- a/data/Oficina_de_procuradora_de_mujeres/opmAgresores.xlsx
+++ b/data/Oficina_de_procuradora_de_mujeres/opmAgresores.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gnper\Documents\ViolenciaGeneroPR\data\Oficina_de_procuradora_de_mujeres\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A22B39B-D4D7-459D-BE27-CE3AAAE1D4F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAC35901-2B18-43A6-A6AD-42B21DDAC80B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13056" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9120" yWindow="1116" windowWidth="11424" windowHeight="9420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -657,7 +657,7 @@
         <v>3</v>
       </c>
       <c r="C23">
-        <v>838</v>
+        <v>994</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -668,7 +668,7 @@
         <v>4</v>
       </c>
       <c r="C24" s="1">
-        <v>21</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -679,7 +679,7 @@
         <v>5</v>
       </c>
       <c r="C25" s="1">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -701,7 +701,7 @@
         <v>7</v>
       </c>
       <c r="C27" s="1">
-        <v>29</v>
+        <v>39</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -712,7 +712,7 @@
         <v>8</v>
       </c>
       <c r="C28" s="1">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">

--- a/data/Oficina_de_procuradora_de_mujeres/opmAgresores.xlsx
+++ b/data/Oficina_de_procuradora_de_mujeres/opmAgresores.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gnper\Documents\ViolenciaGeneroPR\data\Oficina_de_procuradora_de_mujeres\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAC35901-2B18-43A6-A6AD-42B21DDAC80B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D723AE2-BAD5-4FDF-B02B-951903BEA06F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9120" yWindow="1116" windowWidth="11424" windowHeight="9420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9720" yWindow="1716" windowWidth="12132" windowHeight="9384" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -657,7 +657,7 @@
         <v>3</v>
       </c>
       <c r="C23">
-        <v>994</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -668,7 +668,7 @@
         <v>4</v>
       </c>
       <c r="C24" s="1">
-        <v>30</v>
+        <v>37</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -679,7 +679,7 @@
         <v>5</v>
       </c>
       <c r="C25" s="1">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -701,7 +701,7 @@
         <v>7</v>
       </c>
       <c r="C27" s="1">
-        <v>39</v>
+        <v>53</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -712,7 +712,7 @@
         <v>8</v>
       </c>
       <c r="C28" s="1">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
